--- a/data/trans_orig/P0802-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P0802-Edad-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según limitación a subir varios pisos en 2007</t>
+          <t>Población según limitación a subir varios pisos en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>472275</t>
+          <t>473299</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>486756</t>
+          <t>487034</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>95,8%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>446265</t>
+          <t>446919</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>460591</t>
+          <t>461012</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,6%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,61%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>924933</t>
+          <t>925289</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>944817</t>
+          <t>945284</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>96,23%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,31%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6458</t>
+          <t>5793</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>20144</t>
+          <t>19733</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4168</t>
+          <t>3610</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>16639</t>
+          <t>16628</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>12886</t>
+          <t>12837</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>30570</t>
+          <t>31995</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,33%</t>
         </is>
       </c>
     </row>
@@ -964,7 +964,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5406</t>
+          <t>4803</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>941</t>
+          <t>947</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>9362</t>
+          <t>9393</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1864</t>
+          <t>1816</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>10357</t>
+          <t>11212</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1049,7 +1049,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,17%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>701277</t>
+          <t>700590</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>721863</t>
+          <t>721926</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,25%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>575318</t>
+          <t>576019</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>600629</t>
+          <t>601223</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,98%</t>
+          <t>92,09%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>96,12%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1285890</t>
+          <t>1286832</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1316294</t>
+          <t>1317343</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,48%</t>
+          <t>94,55%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>96,79%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8960</t>
+          <t>8364</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>26118</t>
+          <t>26706</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>22506</t>
+          <t>22005</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>46349</t>
+          <t>46393</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>35613</t>
+          <t>35266</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>65113</t>
+          <t>64116</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,71%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2041</t>
+          <t>2406</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13437</t>
+          <t>13790</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>933</t>
+          <t>931</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8427</t>
+          <t>8432</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4313</t>
+          <t>4890</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>16911</t>
+          <t>18231</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,34%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>595234</t>
+          <t>593232</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>616435</t>
+          <t>616329</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>92,89%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>625089</t>
+          <t>624549</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>651519</t>
+          <t>651475</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>90,63%</t>
+          <t>90,55%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>94,46%</t>
+          <t>94,45%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1225869</t>
+          <t>1227168</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1262142</t>
+          <t>1262461</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>92,28%</t>
+          <t>92,38%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>95,04%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12964</t>
+          <t>12810</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>30517</t>
+          <t>30498</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>28764</t>
+          <t>28735</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>53696</t>
+          <t>54234</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>46411</t>
+          <t>46406</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>77498</t>
+          <t>76115</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1848,7 +1848,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,73%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>6118</t>
+          <t>5607</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>19770</t>
+          <t>19484</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>5596</t>
+          <t>5417</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>20313</t>
+          <t>19165</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>14033</t>
+          <t>14320</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>34561</t>
+          <t>33901</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,55%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>451830</t>
+          <t>452621</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>480582</t>
+          <t>481070</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>87,03%</t>
+          <t>87,19%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>92,57%</t>
+          <t>92,67%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>413928</t>
+          <t>415913</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>448333</t>
+          <t>449139</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>80,27%</t>
+          <t>80,66%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>86,95%</t>
+          <t>87,1%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>877166</t>
+          <t>878416</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>920140</t>
+          <t>920088</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>84,77%</t>
+          <t>84,89%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>27156</t>
+          <t>27514</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>52463</t>
+          <t>53113</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>46577</t>
+          <t>46562</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>75709</t>
+          <t>75185</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2269,7 +2269,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>82377</t>
+          <t>81629</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>121421</t>
+          <t>119449</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>11,54%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>7446</t>
+          <t>7032</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>21292</t>
+          <t>20462</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>15018</t>
+          <t>14919</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>34112</t>
+          <t>32720</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>24604</t>
+          <t>25377</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>48922</t>
+          <t>47345</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,58%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>271874</t>
+          <t>274515</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>307035</t>
+          <t>307321</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>70,3%</t>
+          <t>70,99%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>79,4%</t>
+          <t>79,47%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>260670</t>
+          <t>258447</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>296680</t>
+          <t>295855</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>64,52%</t>
+          <t>63,97%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>73,44%</t>
+          <t>73,23%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>543403</t>
+          <t>541791</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>595190</t>
+          <t>592799</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>68,72%</t>
+          <t>68,52%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>75,27%</t>
+          <t>74,97%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>61367</t>
+          <t>61720</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>92731</t>
+          <t>91685</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>15,96%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>23,98%</t>
+          <t>23,71%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>80584</t>
+          <t>80765</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>112927</t>
+          <t>115590</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>27,95%</t>
+          <t>28,61%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>148903</t>
+          <t>149117</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>195783</t>
+          <t>194481</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>18,86%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>24,76%</t>
+          <t>24,6%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>12936</t>
+          <t>13500</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>30310</t>
+          <t>31334</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>19400</t>
+          <t>19337</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>39841</t>
+          <t>40259</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>37394</t>
+          <t>35888</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>64159</t>
+          <t>64989</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,22%</t>
         </is>
       </c>
     </row>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>174150</t>
+          <t>176029</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>205813</t>
+          <t>206478</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3028,12 +3028,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>59,52%</t>
+          <t>60,16%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>70,34%</t>
+          <t>70,57%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>115272</t>
+          <t>115147</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>150692</t>
+          <t>149977</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>33,61%</t>
+          <t>33,58%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>43,94%</t>
+          <t>43,73%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>301201</t>
+          <t>301408</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>349987</t>
+          <t>348857</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>47,39%</t>
+          <t>47,43%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>55,07%</t>
+          <t>54,89%</t>
         </is>
       </c>
     </row>
@@ -3126,12 +3126,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>61372</t>
+          <t>62877</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>91519</t>
+          <t>91669</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3141,12 +3141,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>21,49%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>31,28%</t>
+          <t>31,33%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,12 +3161,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>141518</t>
+          <t>142433</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>177423</t>
+          <t>177738</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3176,12 +3176,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>41,27%</t>
+          <t>41,53%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>51,74%</t>
+          <t>51,83%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>209583</t>
+          <t>213309</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>256338</t>
+          <t>259252</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>32,98%</t>
+          <t>33,56%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>40,34%</t>
+          <t>40,79%</t>
         </is>
       </c>
     </row>
@@ -3239,12 +3239,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>16328</t>
+          <t>16769</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>35206</t>
+          <t>36187</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3254,12 +3254,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,12 +3274,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>40133</t>
+          <t>38269</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>64763</t>
+          <t>64310</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3289,12 +3289,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>63233</t>
+          <t>59949</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>94684</t>
+          <t>92855</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>14,61%</t>
         </is>
       </c>
     </row>
@@ -3469,12 +3469,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>56119</t>
+          <t>54749</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>81628</t>
+          <t>80924</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3484,12 +3484,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>26,74%</t>
+          <t>26,09%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>38,89%</t>
+          <t>38,56%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>51433</t>
+          <t>50780</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>81685</t>
+          <t>80726</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3519,12 +3519,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>15,21%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>24,46%</t>
+          <t>24,18%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>115663</t>
+          <t>114763</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>156371</t>
+          <t>155284</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>21,27%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>28,76%</t>
+          <t>28,56%</t>
         </is>
       </c>
     </row>
@@ -3582,12 +3582,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>84257</t>
+          <t>84735</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>112093</t>
+          <t>111716</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3597,12 +3597,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>40,14%</t>
+          <t>40,37%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>53,41%</t>
+          <t>53,23%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>155225</t>
+          <t>155521</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>193940</t>
+          <t>192680</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3632,12 +3632,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>46,49%</t>
+          <t>46,58%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>58,08%</t>
+          <t>57,7%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>250722</t>
+          <t>250967</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>295865</t>
+          <t>295657</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3667,12 +3667,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>46,11%</t>
+          <t>46,15%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>54,41%</t>
+          <t>54,37%</t>
         </is>
       </c>
     </row>
@@ -3695,12 +3695,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>33977</t>
+          <t>34029</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>57740</t>
+          <t>56184</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3710,12 +3710,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>16,21%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>27,51%</t>
+          <t>26,77%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>77094</t>
+          <t>77526</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>111801</t>
+          <t>113005</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>23,09%</t>
+          <t>23,22%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>33,48%</t>
+          <t>33,84%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>118008</t>
+          <t>117167</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>161216</t>
+          <t>159286</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>21,55%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>29,65%</t>
+          <t>29,29%</t>
         </is>
       </c>
     </row>
@@ -3925,12 +3925,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2781204</t>
+          <t>2780770</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2855843</t>
+          <t>2860304</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3940,12 +3940,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>84,88%</t>
+          <t>84,87%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>87,16%</t>
+          <t>87,3%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2540493</t>
+          <t>2542685</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>2643450</t>
+          <t>2641918</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3975,12 +3975,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>75,18%</t>
+          <t>75,25%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>78,23%</t>
+          <t>78,18%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>5345698</t>
+          <t>5353005</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>5477417</t>
+          <t>5475675</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4010,12 +4010,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>80,32%</t>
+          <t>80,43%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>82,3%</t>
+          <t>82,27%</t>
         </is>
       </c>
     </row>
@@ -4038,12 +4038,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>303585</t>
+          <t>301996</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>372599</t>
+          <t>371394</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4053,12 +4053,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4073,12 +4073,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>528502</t>
+          <t>532418</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>619138</t>
+          <t>623494</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,12 +4088,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>18,45%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4108,12 +4108,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>851342</t>
+          <t>852849</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>963313</t>
+          <t>960674</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,43%</t>
         </is>
       </c>
     </row>
@@ -4151,12 +4151,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>102165</t>
+          <t>101039</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>144279</t>
+          <t>143626</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4166,12 +4166,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4186,12 +4186,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>186830</t>
+          <t>184782</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>243588</t>
+          <t>243533</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4201,7 +4201,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>298915</t>
+          <t>301104</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>372125</t>
+          <t>371522</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4236,12 +4236,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,58%</t>
         </is>
       </c>
     </row>
@@ -4421,7 +4421,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según limitación a subir varios pisos en 2012</t>
+          <t>Población según limitación a subir varios pisos en 2012 (tasa de respuesta: 99,94%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4616,12 +4616,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>437156</t>
+          <t>437546</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>450299</t>
+          <t>449604</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4631,12 +4631,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>96,34%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>406047</t>
+          <t>405206</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>421269</t>
+          <t>421331</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4666,12 +4666,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>94,38%</t>
+          <t>94,18%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4686,12 +4686,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>849367</t>
+          <t>848105</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>868264</t>
+          <t>868118</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4701,12 +4701,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>95,9%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,16%</t>
         </is>
       </c>
     </row>
@@ -4729,12 +4729,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3287</t>
+          <t>3633</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15813</t>
+          <t>15629</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4744,12 +4744,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4764,12 +4764,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5468</t>
+          <t>5389</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18332</t>
+          <t>18998</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4779,12 +4779,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4799,12 +4799,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>11480</t>
+          <t>11506</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>28953</t>
+          <t>28439</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4819,7 +4819,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,22%</t>
         </is>
       </c>
     </row>
@@ -4847,7 +4847,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4360</t>
+          <t>4345</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4877,12 +4877,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1910</t>
+          <t>1907</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>11009</t>
+          <t>10898</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4897,7 +4897,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4912,12 +4912,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1921</t>
+          <t>1985</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>11857</t>
+          <t>12493</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4932,7 +4932,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,41%</t>
         </is>
       </c>
     </row>
@@ -5072,12 +5072,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>648628</t>
+          <t>648297</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>669383</t>
+          <t>669157</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5087,12 +5087,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,4%</t>
+          <t>94,35%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5107,12 +5107,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>571286</t>
+          <t>571134</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>592723</t>
+          <t>592945</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5122,12 +5122,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,61%</t>
+          <t>93,59%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,13%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5142,12 +5142,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1227679</t>
+          <t>1227017</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1256839</t>
+          <t>1256385</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5157,12 +5157,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,63%</t>
+          <t>94,58%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,84%</t>
         </is>
       </c>
     </row>
@@ -5185,12 +5185,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13117</t>
+          <t>13280</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>32325</t>
+          <t>31974</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5200,12 +5200,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5220,12 +5220,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>14940</t>
+          <t>15315</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>35604</t>
+          <t>36494</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5235,12 +5235,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5255,12 +5255,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>33081</t>
+          <t>34019</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>61147</t>
+          <t>60040</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5270,12 +5270,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,63%</t>
         </is>
       </c>
     </row>
@@ -5298,12 +5298,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1879</t>
+          <t>1951</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13428</t>
+          <t>14269</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5313,12 +5313,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5333,12 +5333,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>926</t>
+          <t>934</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7548</t>
+          <t>8601</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5353,7 +5353,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5368,12 +5368,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3833</t>
+          <t>3851</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>16956</t>
+          <t>16301</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5388,7 +5388,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,26%</t>
         </is>
       </c>
     </row>
@@ -5528,12 +5528,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>627675</t>
+          <t>628204</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>652687</t>
+          <t>651837</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>92,31%</t>
+          <t>92,39%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>95,99%</t>
+          <t>95,86%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5563,12 +5563,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>616051</t>
+          <t>617332</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>649708</t>
+          <t>649766</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>86,66%</t>
+          <t>86,84%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>91,4%</t>
+          <t>91,41%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5598,12 +5598,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1254900</t>
+          <t>1254259</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1295860</t>
+          <t>1297477</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>90,23%</t>
+          <t>90,18%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>93,17%</t>
+          <t>93,29%</t>
         </is>
       </c>
     </row>
@@ -5641,12 +5641,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>21624</t>
+          <t>21155</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>43072</t>
+          <t>42252</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5676,12 +5676,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>42056</t>
+          <t>41604</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>69231</t>
+          <t>69640</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5711,12 +5711,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>68499</t>
+          <t>67167</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>103206</t>
+          <t>105018</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,55%</t>
         </is>
       </c>
     </row>
@@ -5754,12 +5754,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>3181</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>16919</t>
+          <t>17141</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5769,12 +5769,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5789,12 +5789,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>13951</t>
+          <t>12804</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>34895</t>
+          <t>33309</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5824,12 +5824,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>19035</t>
+          <t>19953</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>42651</t>
+          <t>43774</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,15%</t>
         </is>
       </c>
     </row>
@@ -5984,12 +5984,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>531850</t>
+          <t>532829</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>563757</t>
+          <t>564626</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>86,53%</t>
+          <t>86,69%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>91,72%</t>
+          <t>91,87%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6019,12 +6019,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>492558</t>
+          <t>493080</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>531764</t>
+          <t>530900</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>79,93%</t>
+          <t>80,02%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>86,3%</t>
+          <t>86,16%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6054,12 +6054,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1037519</t>
+          <t>1037771</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1087592</t>
+          <t>1085470</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>84,3%</t>
+          <t>84,32%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>88,36%</t>
+          <t>88,19%</t>
         </is>
       </c>
     </row>
@@ -6097,12 +6097,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>34659</t>
+          <t>33791</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>60949</t>
+          <t>61776</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6132,12 +6132,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>57372</t>
+          <t>56087</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>90611</t>
+          <t>88248</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6167,12 +6167,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>98598</t>
+          <t>96388</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>140469</t>
+          <t>139434</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>11,33%</t>
         </is>
       </c>
     </row>
@@ -6210,12 +6210,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>10482</t>
+          <t>11323</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>28032</t>
+          <t>30670</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6245,12 +6245,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>21115</t>
+          <t>20269</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>44537</t>
+          <t>41692</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6280,12 +6280,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>36281</t>
+          <t>37077</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>65917</t>
+          <t>64757</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6295,12 +6295,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,26%</t>
         </is>
       </c>
     </row>
@@ -6440,12 +6440,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>320928</t>
+          <t>321703</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>355319</t>
+          <t>356859</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6455,12 +6455,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>75,09%</t>
+          <t>75,27%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>83,13%</t>
+          <t>83,49%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6475,12 +6475,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>262190</t>
+          <t>262676</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>306442</t>
+          <t>304024</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>58,55%</t>
+          <t>58,66%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>68,43%</t>
+          <t>67,89%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6510,12 +6510,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>593320</t>
+          <t>595163</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>651077</t>
+          <t>652701</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6525,12 +6525,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>67,79%</t>
+          <t>68,0%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>74,39%</t>
+          <t>74,58%</t>
         </is>
       </c>
     </row>
@@ -6553,12 +6553,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>46904</t>
+          <t>47458</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>77268</t>
+          <t>78533</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6568,82 +6568,82 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
+          <t>18,37%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>120961</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>104132</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>142139</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>27,01%</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>23,25%</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>31,74%</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t>181985</t>
+        </is>
+      </c>
+      <c r="S21" s="2" t="inlineStr">
+        <is>
+          <t>158256</t>
+        </is>
+      </c>
+      <c r="T21" s="2" t="inlineStr">
+        <is>
+          <t>207852</t>
+        </is>
+      </c>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>20,79%</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
           <t>18,08%</t>
         </is>
       </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>120961</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>102634</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>142500</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>27,01%</t>
-        </is>
-      </c>
-      <c r="O21" s="2" t="inlineStr">
-        <is>
-          <t>22,92%</t>
-        </is>
-      </c>
-      <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t>31,82%</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t>167</t>
-        </is>
-      </c>
-      <c r="R21" s="2" t="inlineStr">
-        <is>
-          <t>181985</t>
-        </is>
-      </c>
-      <c r="S21" s="2" t="inlineStr">
-        <is>
-          <t>160239</t>
-        </is>
-      </c>
-      <c r="T21" s="2" t="inlineStr">
-        <is>
-          <t>209844</t>
-        </is>
-      </c>
-      <c r="U21" s="2" t="inlineStr">
-        <is>
-          <t>20,79%</t>
-        </is>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>18,31%</t>
-        </is>
-      </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>23,98%</t>
+          <t>23,75%</t>
         </is>
       </c>
     </row>
@@ -6666,12 +6666,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>17220</t>
+          <t>17984</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>38939</t>
+          <t>38667</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6681,12 +6681,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6701,12 +6701,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>29993</t>
+          <t>31310</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>56403</t>
+          <t>57391</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6716,12 +6716,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6736,12 +6736,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>54784</t>
+          <t>53555</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>87668</t>
+          <t>87492</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6751,12 +6751,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>10,0%</t>
         </is>
       </c>
     </row>
@@ -6896,12 +6896,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>160885</t>
+          <t>160787</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>197028</t>
+          <t>198836</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6911,12 +6911,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>51,93%</t>
+          <t>51,9%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>63,6%</t>
+          <t>64,18%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6931,12 +6931,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>125715</t>
+          <t>126088</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>161651</t>
+          <t>164603</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>35,51%</t>
+          <t>35,62%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>45,66%</t>
+          <t>46,5%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6966,12 +6966,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>300661</t>
+          <t>300604</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>352017</t>
+          <t>352130</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6981,12 +6981,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>45,3%</t>
+          <t>45,29%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>53,03%</t>
+          <t>53,05%</t>
         </is>
       </c>
     </row>
@@ -7009,12 +7009,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>70354</t>
+          <t>71917</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>104558</t>
+          <t>106029</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7024,12 +7024,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>23,22%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>33,75%</t>
+          <t>34,23%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7044,12 +7044,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>116116</t>
+          <t>116020</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>153532</t>
+          <t>152819</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>32,8%</t>
+          <t>32,77%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>43,37%</t>
+          <t>43,17%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7079,12 +7079,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>197072</t>
+          <t>195824</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>247591</t>
+          <t>247441</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7094,12 +7094,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>29,69%</t>
+          <t>29,5%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>37,3%</t>
+          <t>37,28%</t>
         </is>
       </c>
     </row>
@@ -7122,12 +7122,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>30724</t>
+          <t>29277</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>55759</t>
+          <t>53746</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>17,35%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7157,12 +7157,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>61283</t>
+          <t>61677</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>91559</t>
+          <t>93254</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>25,86%</t>
+          <t>26,34%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7192,12 +7192,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>99018</t>
+          <t>96900</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>139419</t>
+          <t>137664</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7207,12 +7207,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>21,0%</t>
+          <t>20,74%</t>
         </is>
       </c>
     </row>
@@ -7352,12 +7352,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>57876</t>
+          <t>57869</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>88021</t>
+          <t>89973</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7372,7 +7372,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>35,23%</t>
+          <t>36,01%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7387,12 +7387,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>50411</t>
+          <t>50603</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>80623</t>
+          <t>80182</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>20,67%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7422,12 +7422,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>114929</t>
+          <t>116202</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>160027</t>
+          <t>159068</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7437,12 +7437,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>18,02%</t>
+          <t>18,22%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>25,09%</t>
+          <t>24,94%</t>
         </is>
       </c>
     </row>
@@ -7465,12 +7465,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>88267</t>
+          <t>86924</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>121065</t>
+          <t>119810</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>35,33%</t>
+          <t>34,79%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>48,45%</t>
+          <t>47,95%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7500,12 +7500,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>133632</t>
+          <t>135043</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>173268</t>
+          <t>173924</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7515,12 +7515,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>34,45%</t>
+          <t>34,81%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>44,67%</t>
+          <t>44,84%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>233983</t>
+          <t>229187</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>286051</t>
+          <t>283117</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7550,12 +7550,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>36,69%</t>
+          <t>35,94%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>44,85%</t>
+          <t>44,39%</t>
         </is>
       </c>
     </row>
@@ -7578,12 +7578,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>59027</t>
+          <t>57934</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>90366</t>
+          <t>90096</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7593,12 +7593,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>23,19%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>36,17%</t>
+          <t>36,06%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7613,12 +7613,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>150470</t>
+          <t>147869</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>191306</t>
+          <t>188529</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7628,12 +7628,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>38,79%</t>
+          <t>38,12%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>49,32%</t>
+          <t>48,6%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7648,12 +7648,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>217239</t>
+          <t>216768</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>269313</t>
+          <t>271108</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7663,12 +7663,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>34,06%</t>
+          <t>33,99%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>42,23%</t>
+          <t>42,51%</t>
         </is>
       </c>
     </row>
@@ -7808,12 +7808,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2843764</t>
+          <t>2847280</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2930525</t>
+          <t>2935148</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7823,12 +7823,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>83,08%</t>
+          <t>83,18%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>85,62%</t>
+          <t>85,75%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7843,12 +7843,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2587845</t>
+          <t>2588235</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>2699763</t>
+          <t>2693905</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7858,12 +7858,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>72,75%</t>
+          <t>72,76%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>75,9%</t>
+          <t>75,73%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7878,12 +7878,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>5468649</t>
+          <t>5464932</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>5601630</t>
+          <t>5599342</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7893,12 +7893,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>78,35%</t>
+          <t>78,29%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>80,25%</t>
+          <t>80,22%</t>
         </is>
       </c>
     </row>
@@ -7921,12 +7921,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>327119</t>
+          <t>321248</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>397194</t>
+          <t>396264</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -7936,12 +7936,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -7956,12 +7956,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>524396</t>
+          <t>529916</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>612693</t>
+          <t>615914</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -7971,12 +7971,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>17,31%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -7991,12 +7991,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>873280</t>
+          <t>873010</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>985866</t>
+          <t>986556</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -8011,7 +8011,7 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>14,13%</t>
         </is>
       </c>
     </row>
@@ -8034,12 +8034,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>148422</t>
+          <t>147007</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>203522</t>
+          <t>202521</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8049,12 +8049,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8069,12 +8069,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>312034</t>
+          <t>313393</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>380918</t>
+          <t>385717</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8104,12 +8104,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>474979</t>
+          <t>482134</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>570104</t>
+          <t>568634</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8119,12 +8119,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,15%</t>
         </is>
       </c>
     </row>
@@ -8304,7 +8304,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según limitación a subir varios pisos en 2016</t>
+          <t>Población según limitación a subir varios pisos en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8499,12 +8499,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>409456</t>
+          <t>410492</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>418494</t>
+          <t>418498</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8514,7 +8514,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -8539,7 +8539,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>387676</t>
+          <t>388110</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8554,7 +8554,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>786960</t>
+          <t>788466</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>804376</t>
+          <t>805467</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8584,12 +8584,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>96,53%</t>
+          <t>96,72%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,8%</t>
         </is>
       </c>
     </row>
@@ -8612,12 +8612,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>969</t>
+          <t>965</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10007</t>
+          <t>8971</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8632,7 +8632,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8647,12 +8647,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7095</t>
+          <t>7340</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>21146</t>
+          <t>21162</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8662,12 +8662,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8682,12 +8682,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>10035</t>
+          <t>9130</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>26965</t>
+          <t>25157</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8697,12 +8697,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,09%</t>
         </is>
       </c>
     </row>
@@ -8725,97 +8725,97 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>1026</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>2044</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>5788</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>0,26%</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>0,49%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>1,46%</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="R6" s="2" t="inlineStr">
         <is>
           <t>1026</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr">
+      <c r="S6" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>5177</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>0,26%</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>5802</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>0,13%</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>1,31%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>1026</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>5134</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>0,13%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,71%</t>
         </is>
       </c>
     </row>
@@ -8955,12 +8955,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>564662</t>
+          <t>565378</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>581041</t>
+          <t>581612</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8970,12 +8970,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,63%</t>
+          <t>95,75%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8990,12 +8990,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>527770</t>
+          <t>527103</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>547027</t>
+          <t>547894</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9005,12 +9005,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,65%</t>
+          <t>93,53%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>97,22%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9025,12 +9025,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1099046</t>
+          <t>1098381</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1124701</t>
+          <t>1124255</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9040,12 +9040,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>95,18%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,42%</t>
         </is>
       </c>
     </row>
@@ -9068,12 +9068,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8066</t>
+          <t>7462</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>23145</t>
+          <t>22970</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9083,12 +9083,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -9103,12 +9103,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>8982</t>
+          <t>8279</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>24584</t>
+          <t>24341</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9118,12 +9118,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -9138,12 +9138,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>19734</t>
+          <t>20193</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>42208</t>
+          <t>42228</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9153,7 +9153,7 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
@@ -9186,7 +9186,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6610</t>
+          <t>7336</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9201,7 +9201,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9216,12 +9216,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4280</t>
+          <t>4634</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>17105</t>
+          <t>17820</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9231,12 +9231,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9251,12 +9251,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5785</t>
+          <t>6134</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>20321</t>
+          <t>20237</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9266,12 +9266,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,75%</t>
         </is>
       </c>
     </row>
@@ -9411,12 +9411,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>620452</t>
+          <t>619785</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>643001</t>
+          <t>643067</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>92,73%</t>
+          <t>92,63%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>96,11%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9446,12 +9446,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>598865</t>
+          <t>598275</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>625655</t>
+          <t>625437</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9461,12 +9461,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>90,55%</t>
+          <t>90,46%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>94,6%</t>
+          <t>94,56%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9481,12 +9481,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1226845</t>
+          <t>1227670</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1264311</t>
+          <t>1263642</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9496,12 +9496,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>92,21%</t>
+          <t>92,27%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>95,03%</t>
+          <t>94,98%</t>
         </is>
       </c>
     </row>
@@ -9524,12 +9524,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>20408</t>
+          <t>20016</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>41341</t>
+          <t>41602</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9539,12 +9539,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9559,12 +9559,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>29965</t>
+          <t>29310</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>55213</t>
+          <t>55450</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9574,12 +9574,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9594,12 +9594,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>54156</t>
+          <t>53825</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>87893</t>
+          <t>87435</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9609,12 +9609,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,57%</t>
         </is>
       </c>
     </row>
@@ -9637,12 +9637,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2982</t>
+          <t>3030</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>14368</t>
+          <t>14615</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9657,7 +9657,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9672,12 +9672,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2836</t>
+          <t>2823</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>13798</t>
+          <t>13424</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9692,7 +9692,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9707,12 +9707,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>7930</t>
+          <t>8032</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>22878</t>
+          <t>22895</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9867,12 +9867,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>550371</t>
+          <t>548123</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>585269</t>
+          <t>583891</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>85,19%</t>
+          <t>84,84%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>90,59%</t>
+          <t>90,38%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>533065</t>
+          <t>535051</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>570888</t>
+          <t>570699</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>82,13%</t>
+          <t>82,43%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>87,95%</t>
+          <t>87,92%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9937,12 +9937,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1097823</t>
+          <t>1097337</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1146860</t>
+          <t>1146808</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9952,7 +9952,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>84,77%</t>
+          <t>84,73%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -9980,12 +9980,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>33077</t>
+          <t>34118</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>61319</t>
+          <t>61686</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9995,12 +9995,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10015,12 +10015,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>42120</t>
+          <t>42195</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>71127</t>
+          <t>70183</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10030,12 +10030,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10050,12 +10050,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>81369</t>
+          <t>82471</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>120379</t>
+          <t>121506</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10065,12 +10065,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,38%</t>
         </is>
       </c>
     </row>
@@ -10093,12 +10093,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>22506</t>
+          <t>22167</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>46404</t>
+          <t>45086</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10108,12 +10108,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -10128,12 +10128,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>28717</t>
+          <t>29746</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>53478</t>
+          <t>52970</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10143,12 +10143,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -10163,12 +10163,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>56651</t>
+          <t>56683</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>91521</t>
+          <t>90983</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10178,12 +10178,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,03%</t>
         </is>
       </c>
     </row>
@@ -10323,12 +10323,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>361301</t>
+          <t>359566</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>398040</t>
+          <t>398587</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10338,12 +10338,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>75,6%</t>
+          <t>75,24%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>83,29%</t>
+          <t>83,4%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10358,12 +10358,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>315249</t>
+          <t>314819</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>359829</t>
+          <t>358508</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>63,45%</t>
+          <t>63,36%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>72,42%</t>
+          <t>72,16%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10393,12 +10393,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>687184</t>
+          <t>688323</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>747082</t>
+          <t>749687</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10408,12 +10408,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>70,5%</t>
+          <t>70,61%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>76,64%</t>
+          <t>76,91%</t>
         </is>
       </c>
     </row>
@@ -10436,12 +10436,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>60643</t>
+          <t>61057</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>94152</t>
+          <t>96050</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10451,12 +10451,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>20,1%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10471,12 +10471,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>82325</t>
+          <t>81691</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>117649</t>
+          <t>117152</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10486,12 +10486,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>23,68%</t>
+          <t>23,58%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10506,12 +10506,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>152821</t>
+          <t>150861</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>203941</t>
+          <t>202770</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10521,12 +10521,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>20,8%</t>
         </is>
       </c>
     </row>
@@ -10549,12 +10549,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>13312</t>
+          <t>12371</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>33475</t>
+          <t>32023</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10564,12 +10564,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10584,12 +10584,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>45609</t>
+          <t>45986</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>76547</t>
+          <t>75885</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10599,12 +10599,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10619,12 +10619,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>62622</t>
+          <t>63312</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>99725</t>
+          <t>101997</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10634,12 +10634,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,46%</t>
         </is>
       </c>
     </row>
@@ -10779,12 +10779,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>201672</t>
+          <t>202645</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>235853</t>
+          <t>236985</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>60,32%</t>
+          <t>60,61%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>70,54%</t>
+          <t>70,88%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10814,12 +10814,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>175864</t>
+          <t>177604</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>217532</t>
+          <t>216598</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10829,12 +10829,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>46,55%</t>
+          <t>47,01%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>57,58%</t>
+          <t>57,34%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10849,12 +10849,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>388732</t>
+          <t>389136</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>443241</t>
+          <t>442334</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10864,12 +10864,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>54,59%</t>
+          <t>54,65%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>62,24%</t>
+          <t>62,12%</t>
         </is>
       </c>
     </row>
@@ -10892,12 +10892,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>59952</t>
+          <t>60538</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>90799</t>
+          <t>92210</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10907,12 +10907,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>18,11%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>27,16%</t>
+          <t>27,58%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10927,12 +10927,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>103563</t>
+          <t>103638</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>141083</t>
+          <t>140138</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10942,12 +10942,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>27,41%</t>
+          <t>27,43%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>37,35%</t>
+          <t>37,1%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10962,12 +10962,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>174736</t>
+          <t>173794</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>223433</t>
+          <t>224386</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10977,12 +10977,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>24,54%</t>
+          <t>24,41%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>31,38%</t>
+          <t>31,51%</t>
         </is>
       </c>
     </row>
@@ -11005,12 +11005,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>28525</t>
+          <t>28403</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>53252</t>
+          <t>53253</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -11020,7 +11020,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -11040,12 +11040,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>45263</t>
+          <t>45460</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>73555</t>
+          <t>74135</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -11055,12 +11055,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>19,62%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -11075,12 +11075,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>78603</t>
+          <t>79898</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>115367</t>
+          <t>115884</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -11090,12 +11090,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>16,27%</t>
         </is>
       </c>
     </row>
@@ -11235,12 +11235,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>95093</t>
+          <t>96221</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>124749</t>
+          <t>122476</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -11250,12 +11250,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>37,0%</t>
+          <t>37,44%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>48,54%</t>
+          <t>47,66%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -11270,12 +11270,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>92865</t>
+          <t>92819</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>131869</t>
+          <t>136338</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -11285,12 +11285,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>23,21%</t>
+          <t>23,19%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>32,95%</t>
+          <t>34,07%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -11305,12 +11305,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>196796</t>
+          <t>197096</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>251044</t>
+          <t>246266</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -11320,12 +11320,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>29,95%</t>
+          <t>29,99%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>38,2%</t>
+          <t>37,47%</t>
         </is>
       </c>
     </row>
@@ -11348,12 +11348,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>81470</t>
+          <t>80992</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>108103</t>
+          <t>108936</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -11363,12 +11363,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>31,7%</t>
+          <t>31,51%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>42,06%</t>
+          <t>42,39%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -11383,12 +11383,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>127043</t>
+          <t>124037</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>169794</t>
+          <t>167474</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -11398,12 +11398,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>31,75%</t>
+          <t>31,0%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>42,43%</t>
+          <t>41,85%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -11418,12 +11418,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>215292</t>
+          <t>220327</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>267957</t>
+          <t>269531</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -11433,12 +11433,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>32,76%</t>
+          <t>33,53%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>40,77%</t>
+          <t>41,01%</t>
         </is>
       </c>
     </row>
@@ -11461,12 +11461,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>41950</t>
+          <t>41842</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>64244</t>
+          <t>65841</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -11476,12 +11476,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>25,62%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11496,12 +11496,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>119470</t>
+          <t>120383</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>162420</t>
+          <t>162224</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11511,12 +11511,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>29,85%</t>
+          <t>30,08%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>40,59%</t>
+          <t>40,54%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11531,12 +11531,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>168709</t>
+          <t>168014</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>219466</t>
+          <t>217439</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11546,12 +11546,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>25,67%</t>
+          <t>25,57%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>33,4%</t>
+          <t>33,09%</t>
         </is>
       </c>
     </row>
@@ -11691,12 +11691,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2858151</t>
+          <t>2857004</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2942999</t>
+          <t>2944841</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11706,12 +11706,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>84,2%</t>
+          <t>84,17%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>86,7%</t>
+          <t>86,76%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11726,12 +11726,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2680789</t>
+          <t>2682849</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>2784995</t>
+          <t>2784478</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11741,12 +11741,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>75,63%</t>
+          <t>75,69%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>78,57%</t>
+          <t>78,56%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11761,12 +11761,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>5571243</t>
+          <t>5573243</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>5711331</t>
+          <t>5708616</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11776,12 +11776,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>80,29%</t>
+          <t>80,32%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>82,31%</t>
+          <t>82,27%</t>
         </is>
       </c>
     </row>
@@ -11804,12 +11804,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>303229</t>
+          <t>303815</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>376772</t>
+          <t>375847</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -11839,12 +11839,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>452231</t>
+          <t>452050</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>537256</t>
+          <t>542378</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -11854,12 +11854,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -11874,12 +11874,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>777451</t>
+          <t>777516</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>886340</t>
+          <t>884242</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -11889,12 +11889,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>12,74%</t>
         </is>
       </c>
     </row>
@@ -11917,12 +11917,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>131633</t>
+          <t>131610</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>179169</t>
+          <t>179052</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -11937,7 +11937,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -11952,12 +11952,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>284283</t>
+          <t>279409</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>354970</t>
+          <t>355076</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -11967,12 +11967,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -11987,12 +11987,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>423935</t>
+          <t>426191</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>515728</t>
+          <t>511439</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -12002,12 +12002,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,37%</t>
         </is>
       </c>
     </row>
@@ -12187,7 +12187,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según limitación a subir varios pisos en 2023</t>
+          <t>Población según limitación a subir varios pisos en 2023 (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -12382,7 +12382,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>375098</t>
+          <t>378638</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -12397,7 +12397,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>94,66%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -12417,12 +12417,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>296236</t>
+          <t>295726</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>311291</t>
+          <t>311402</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -12432,12 +12432,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>94,58%</t>
+          <t>94,42%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,43%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -12452,12 +12452,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>685844</t>
+          <t>684782</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>708718</t>
+          <t>707982</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>96,02%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,27%</t>
         </is>
       </c>
     </row>
@@ -12500,7 +12500,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>24889</t>
+          <t>21349</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -12515,7 +12515,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -12530,12 +12530,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1352</t>
+          <t>1162</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>15370</t>
+          <t>15368</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -12545,7 +12545,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -12565,12 +12565,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>3374</t>
+          <t>3945</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>26950</t>
+          <t>26812</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,76%</t>
         </is>
       </c>
     </row>
@@ -12608,82 +12608,82 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>1621</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>4435</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>8892</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>0,52%</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>1,11%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>2,84%</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="R6" s="2" t="inlineStr">
         <is>
           <t>1621</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr">
+      <c r="S6" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>7974</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>0,52%</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>2,55%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>1621</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>9830</t>
+          <t>9864</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -12838,12 +12838,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>398696</t>
+          <t>397370</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>416154</t>
+          <t>415793</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -12853,12 +12853,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>93,82%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -12873,7 +12873,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>498950</t>
+          <t>498328</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -12888,7 +12888,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>901736</t>
+          <t>900429</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>924047</t>
+          <t>922882</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,24%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,64%</t>
         </is>
       </c>
     </row>
@@ -12951,12 +12951,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4219</t>
+          <t>3957</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>19498</t>
+          <t>20427</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -12966,12 +12966,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -12986,12 +12986,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1892</t>
+          <t>1981</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>11655</t>
+          <t>12398</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -13001,12 +13001,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -13021,12 +13021,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>8322</t>
+          <t>8194</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>27450</t>
+          <t>27613</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -13036,12 +13036,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,95%</t>
         </is>
       </c>
     </row>
@@ -13064,12 +13064,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1182</t>
+          <t>1186</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11239</t>
+          <t>11485</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -13084,7 +13084,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -13104,7 +13104,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4552</t>
+          <t>5367</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -13119,7 +13119,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -13134,12 +13134,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2070</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>12432</t>
+          <t>12939</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -13154,7 +13154,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,38%</t>
         </is>
       </c>
     </row>
@@ -13294,12 +13294,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>494832</t>
+          <t>493445</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>515750</t>
+          <t>516139</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -13309,12 +13309,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>92,26%</t>
+          <t>92,0%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>96,23%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -13329,12 +13329,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>541573</t>
+          <t>540490</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>563473</t>
+          <t>563963</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -13344,12 +13344,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>91,57%</t>
+          <t>91,38%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>95,27%</t>
+          <t>95,35%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -13364,12 +13364,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1042466</t>
+          <t>1041963</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1074110</t>
+          <t>1073701</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -13379,12 +13379,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>92,43%</t>
+          <t>92,39%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>95,2%</t>
         </is>
       </c>
     </row>
@@ -13407,12 +13407,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17151</t>
+          <t>16440</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>37057</t>
+          <t>37115</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -13422,12 +13422,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -13442,12 +13442,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>19274</t>
+          <t>19642</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>38407</t>
+          <t>39105</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -13457,12 +13457,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -13477,12 +13477,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>42051</t>
+          <t>41120</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>69572</t>
+          <t>68942</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -13492,12 +13492,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,11%</t>
         </is>
       </c>
     </row>
@@ -13520,12 +13520,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1318</t>
+          <t>1297</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>11656</t>
+          <t>12067</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -13535,12 +13535,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -13555,12 +13555,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>5588</t>
+          <t>5663</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>16745</t>
+          <t>16614</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -13570,12 +13570,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -13590,12 +13590,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>9016</t>
+          <t>8844</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>24053</t>
+          <t>23019</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -13605,12 +13605,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,04%</t>
         </is>
       </c>
     </row>
@@ -13750,12 +13750,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>254759</t>
+          <t>240454</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>795770</t>
+          <t>795158</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>28,7%</t>
+          <t>27,08%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>89,64%</t>
+          <t>89,57%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -13785,12 +13785,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>605240</t>
+          <t>605902</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>642827</t>
+          <t>640813</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -13800,12 +13800,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>84,9%</t>
+          <t>84,99%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>90,17%</t>
+          <t>89,89%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -13820,12 +13820,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>706974</t>
+          <t>796784</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1418843</t>
+          <t>1420092</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -13835,12 +13835,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>44,17%</t>
+          <t>49,78%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>88,64%</t>
+          <t>88,72%</t>
         </is>
       </c>
     </row>
@@ -13863,12 +13863,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>55063</t>
+          <t>56955</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>618285</t>
+          <t>636801</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -13878,12 +13878,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>69,64%</t>
+          <t>71,73%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -13898,12 +13898,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>49699</t>
+          <t>51087</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>84900</t>
+          <t>83861</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -13913,12 +13913,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -13933,12 +13933,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>123718</t>
+          <t>122627</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>872588</t>
+          <t>771104</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -13948,12 +13948,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>54,51%</t>
+          <t>48,17%</t>
         </is>
       </c>
     </row>
@@ -13976,12 +13976,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>10135</t>
+          <t>11288</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>43598</t>
+          <t>44075</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -13991,12 +13991,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -14011,12 +14011,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>16177</t>
+          <t>15770</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>33654</t>
+          <t>31620</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -14026,12 +14026,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -14046,12 +14046,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>30335</t>
+          <t>30311</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>68299</t>
+          <t>69180</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -14061,12 +14061,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,32%</t>
         </is>
       </c>
     </row>
@@ -14206,12 +14206,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>421127</t>
+          <t>422475</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>458442</t>
+          <t>459093</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -14221,12 +14221,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>75,04%</t>
+          <t>75,28%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>81,68%</t>
+          <t>81,8%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -14241,12 +14241,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>393271</t>
+          <t>394177</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>423974</t>
+          <t>423653</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -14256,12 +14256,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>71,78%</t>
+          <t>71,94%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>77,38%</t>
+          <t>77,32%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -14276,12 +14276,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>823740</t>
+          <t>826053</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>873719</t>
+          <t>872723</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -14291,12 +14291,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>74,27%</t>
+          <t>74,48%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>78,77%</t>
+          <t>78,68%</t>
         </is>
       </c>
     </row>
@@ -14319,12 +14319,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>73713</t>
+          <t>72763</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>106918</t>
+          <t>106159</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -14334,12 +14334,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>18,92%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -14354,12 +14354,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>87293</t>
+          <t>86900</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>113354</t>
+          <t>113312</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -14369,12 +14369,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>15,86%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>20,68%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -14389,12 +14389,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>169775</t>
+          <t>169124</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>211808</t>
+          <t>210858</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -14404,12 +14404,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,25%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>19,01%</t>
         </is>
       </c>
     </row>
@@ -14432,12 +14432,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>22453</t>
+          <t>22379</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>44327</t>
+          <t>43088</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -14447,12 +14447,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -14467,12 +14467,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>31007</t>
+          <t>30515</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>48419</t>
+          <t>48078</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -14482,12 +14482,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -14502,12 +14502,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>57727</t>
+          <t>57384</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>83420</t>
+          <t>84904</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -14517,12 +14517,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,65%</t>
         </is>
       </c>
     </row>
@@ -14662,12 +14662,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>259194</t>
+          <t>260068</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>285818</t>
+          <t>285936</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -14677,12 +14677,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>70,54%</t>
+          <t>70,78%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>77,79%</t>
+          <t>77,82%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -14697,12 +14697,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>354283</t>
+          <t>355698</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>539173</t>
+          <t>535618</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -14712,12 +14712,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>58,24%</t>
+          <t>58,47%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>88,63%</t>
+          <t>88,04%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -14732,12 +14732,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>642471</t>
+          <t>642448</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>852473</t>
+          <t>842441</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -14752,7 +14752,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>87,36%</t>
+          <t>86,33%</t>
         </is>
       </c>
     </row>
@@ -14775,12 +14775,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>54444</t>
+          <t>55137</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>78723</t>
+          <t>78876</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -14790,12 +14790,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>21,47%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -14810,12 +14810,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>49062</t>
+          <t>52935</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>187230</t>
+          <t>187492</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -14825,12 +14825,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>30,78%</t>
+          <t>30,82%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -14845,12 +14845,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>90906</t>
+          <t>94106</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>243754</t>
+          <t>241830</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -14860,12 +14860,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>24,98%</t>
+          <t>24,78%</t>
         </is>
       </c>
     </row>
@@ -14888,12 +14888,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>19939</t>
+          <t>19664</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>35835</t>
+          <t>35795</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -14903,12 +14903,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -14923,12 +14923,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>17570</t>
+          <t>19067</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>70028</t>
+          <t>69612</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -14938,12 +14938,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -14958,12 +14958,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>36080</t>
+          <t>37246</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>94506</t>
+          <t>94541</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -14973,7 +14973,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -15118,12 +15118,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>115309</t>
+          <t>116065</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>140545</t>
+          <t>142426</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -15133,12 +15133,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>40,78%</t>
+          <t>41,05%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>49,7%</t>
+          <t>50,37%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -15153,12 +15153,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>81893</t>
+          <t>83454</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>105656</t>
+          <t>107239</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -15168,12 +15168,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>19,62%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>24,85%</t>
+          <t>25,22%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -15188,12 +15188,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>205161</t>
+          <t>204749</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>241143</t>
+          <t>241248</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -15203,12 +15203,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>28,98%</t>
+          <t>28,92%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>34,06%</t>
+          <t>34,07%</t>
         </is>
       </c>
     </row>
@@ -15231,12 +15231,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>85280</t>
+          <t>86036</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>110696</t>
+          <t>112628</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -15246,12 +15246,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>30,16%</t>
+          <t>30,43%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>39,15%</t>
+          <t>39,83%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -15266,12 +15266,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>159160</t>
+          <t>158257</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>187757</t>
+          <t>186752</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -15281,12 +15281,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>37,43%</t>
+          <t>37,21%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>44,15%</t>
+          <t>43,91%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -15301,12 +15301,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>252465</t>
+          <t>251015</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>290639</t>
+          <t>290356</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -15316,12 +15316,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>35,66%</t>
+          <t>35,45%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>41,05%</t>
+          <t>41,01%</t>
         </is>
       </c>
     </row>
@@ -15344,12 +15344,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>45718</t>
+          <t>46364</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>66383</t>
+          <t>67530</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -15359,12 +15359,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>23,48%</t>
+          <t>23,88%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -15379,12 +15379,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>144902</t>
+          <t>143847</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>173509</t>
+          <t>172441</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -15394,12 +15394,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>34,07%</t>
+          <t>33,83%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>40,8%</t>
+          <t>40,55%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -15414,12 +15414,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>195461</t>
+          <t>196223</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>231908</t>
+          <t>232499</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -15429,12 +15429,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>27,61%</t>
+          <t>27,71%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>32,75%</t>
+          <t>32,84%</t>
         </is>
       </c>
     </row>
@@ -15574,12 +15574,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2130097</t>
+          <t>2136835</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2946401</t>
+          <t>2946868</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -15589,12 +15589,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>61,58%</t>
+          <t>61,77%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>85,18%</t>
+          <t>85,19%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -15609,12 +15609,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2867523</t>
+          <t>2867724</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>3084092</t>
+          <t>3085463</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -15629,7 +15629,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>83,1%</t>
+          <t>83,14%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -15644,12 +15644,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>4915696</t>
+          <t>5087714</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>5898884</t>
+          <t>5904243</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -15659,12 +15659,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>68,56%</t>
+          <t>70,96%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>82,27%</t>
+          <t>82,34%</t>
         </is>
       </c>
     </row>
@@ -15687,12 +15687,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>354394</t>
+          <t>353796</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>1217135</t>
+          <t>1210510</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -15702,12 +15702,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>35,19%</t>
+          <t>35,0%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -15722,12 +15722,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>410088</t>
+          <t>405299</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>547076</t>
+          <t>547031</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -15737,7 +15737,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -15757,12 +15757,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>840011</t>
+          <t>836345</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>1870835</t>
+          <t>1789488</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -15772,12 +15772,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>26,09%</t>
+          <t>24,96%</t>
         </is>
       </c>
     </row>
@@ -15800,12 +15800,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>117959</t>
+          <t>118386</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>176816</t>
+          <t>177154</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -15815,12 +15815,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -15835,12 +15835,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>221814</t>
+          <t>226646</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>309173</t>
+          <t>308848</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -15850,12 +15850,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -15870,12 +15870,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>367088</t>
+          <t>371618</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>470483</t>
+          <t>472988</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -15885,12 +15885,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,6%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P0802-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P0802-Edad-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>473299</t>
+          <t>473226</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>487034</t>
+          <t>487290</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>95,78%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,63%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>446919</t>
+          <t>446754</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>461012</t>
+          <t>461113</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>95,56%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>925289</t>
+          <t>924309</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>945284</t>
+          <t>944873</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>96,23%</t>
+          <t>96,13%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,27%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5793</t>
+          <t>6501</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19733</t>
+          <t>19885</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3610</t>
+          <t>3851</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>16628</t>
+          <t>16514</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>12837</t>
+          <t>12791</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>31995</t>
+          <t>32042</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4803</t>
+          <t>4844</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>947</t>
+          <t>933</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>9393</t>
+          <t>9341</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1816</t>
+          <t>1852</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>11212</t>
+          <t>10418</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1049,7 +1049,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,08%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>700590</t>
+          <t>701130</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>721926</t>
+          <t>721817</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>95,33%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>576019</t>
+          <t>576814</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>601223</t>
+          <t>601023</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,09%</t>
+          <t>92,22%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1286832</t>
+          <t>1284348</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1317343</t>
+          <t>1317451</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>94,37%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,8%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8364</t>
+          <t>8976</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>26706</t>
+          <t>26795</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>22005</t>
+          <t>22497</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>46393</t>
+          <t>46025</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>35266</t>
+          <t>34990</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>64116</t>
+          <t>66719</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,9%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2406</t>
+          <t>2419</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13790</t>
+          <t>13181</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>931</t>
+          <t>934</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8432</t>
+          <t>9512</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1470,42 +1470,42 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
+          <t>1,52%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>9491</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>4885</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>18376</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>0,36%</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
           <t>1,35%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>9491</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>4890</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>18231</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,7%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,36%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>1,34%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>593232</t>
+          <t>595199</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>616329</t>
+          <t>617415</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>92,89%</t>
+          <t>93,19%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,67%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>624549</t>
+          <t>624500</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>651475</t>
+          <t>651366</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>90,55%</t>
+          <t>90,54%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>94,44%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1227168</t>
+          <t>1227270</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1262461</t>
+          <t>1263112</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>92,38%</t>
+          <t>92,39%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>95,04%</t>
+          <t>95,08%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12810</t>
+          <t>12659</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>30498</t>
+          <t>30472</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>28735</t>
+          <t>28994</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>54234</t>
+          <t>53633</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>46406</t>
+          <t>46139</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>76115</t>
+          <t>77381</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,83%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5607</t>
+          <t>6160</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>19484</t>
+          <t>19046</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>5417</t>
+          <t>5717</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>19165</t>
+          <t>19269</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>14320</t>
+          <t>13509</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>33901</t>
+          <t>32913</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,48%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>452621</t>
+          <t>451566</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>481070</t>
+          <t>480302</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>87,19%</t>
+          <t>86,98%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>92,67%</t>
+          <t>92,52%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>415913</t>
+          <t>415142</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>449139</t>
+          <t>448540</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>80,66%</t>
+          <t>80,51%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>87,1%</t>
+          <t>86,99%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>878416</t>
+          <t>878618</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>920088</t>
+          <t>921234</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>84,89%</t>
+          <t>84,91%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>88,92%</t>
+          <t>89,03%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>27514</t>
+          <t>26714</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>53113</t>
+          <t>53230</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>46562</t>
+          <t>47250</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>75185</t>
+          <t>76804</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>14,89%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>81629</t>
+          <t>81135</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>119449</t>
+          <t>119982</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,59%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>7032</t>
+          <t>6867</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>20462</t>
+          <t>21004</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>14919</t>
+          <t>14376</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>32720</t>
+          <t>31646</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>25377</t>
+          <t>25291</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>47345</t>
+          <t>49482</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,78%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>274515</t>
+          <t>274686</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>307321</t>
+          <t>306398</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>70,99%</t>
+          <t>71,03%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>79,47%</t>
+          <t>79,23%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>258447</t>
+          <t>261518</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>295855</t>
+          <t>298801</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>63,97%</t>
+          <t>64,73%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>73,23%</t>
+          <t>73,96%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>541791</t>
+          <t>542669</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>592799</t>
+          <t>593465</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>68,52%</t>
+          <t>68,63%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>74,97%</t>
+          <t>75,06%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>61720</t>
+          <t>61194</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>91685</t>
+          <t>90430</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>15,82%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>23,38%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>80765</t>
+          <t>79005</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>115590</t>
+          <t>114389</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>19,56%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>28,61%</t>
+          <t>28,32%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>149117</t>
+          <t>150214</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>194481</t>
+          <t>195110</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>24,68%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>13500</t>
+          <t>12254</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>31334</t>
+          <t>30332</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>19337</t>
+          <t>18991</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>40259</t>
+          <t>40319</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>35888</t>
+          <t>37080</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>64989</t>
+          <t>63686</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,05%</t>
         </is>
       </c>
     </row>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>176029</t>
+          <t>176185</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>206478</t>
+          <t>205800</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3028,12 +3028,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>60,16%</t>
+          <t>60,22%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>70,57%</t>
+          <t>70,34%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>115147</t>
+          <t>115700</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>149977</t>
+          <t>152033</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>33,58%</t>
+          <t>33,74%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>43,73%</t>
+          <t>44,33%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>301408</t>
+          <t>300730</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>348857</t>
+          <t>349764</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>47,43%</t>
+          <t>47,32%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>54,89%</t>
+          <t>55,04%</t>
         </is>
       </c>
     </row>
@@ -3126,12 +3126,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>62877</t>
+          <t>63340</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>91669</t>
+          <t>91629</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3141,12 +3141,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>21,49%</t>
+          <t>21,65%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>31,33%</t>
+          <t>31,32%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,12 +3161,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>142433</t>
+          <t>139623</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>177738</t>
+          <t>177274</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3176,12 +3176,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>41,53%</t>
+          <t>40,71%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>51,83%</t>
+          <t>51,69%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>213309</t>
+          <t>208861</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>259252</t>
+          <t>257405</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>33,56%</t>
+          <t>32,86%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>40,79%</t>
+          <t>40,5%</t>
         </is>
       </c>
     </row>
@@ -3239,12 +3239,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>16769</t>
+          <t>16780</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>36187</t>
+          <t>34862</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3254,12 +3254,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,12 +3274,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>38269</t>
+          <t>39086</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>64310</t>
+          <t>65091</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3289,12 +3289,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>18,98%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>59949</t>
+          <t>60790</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>92855</t>
+          <t>92887</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>14,62%</t>
         </is>
       </c>
     </row>
@@ -3469,12 +3469,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>54749</t>
+          <t>55583</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>80924</t>
+          <t>81037</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3484,12 +3484,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>26,09%</t>
+          <t>26,48%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>38,56%</t>
+          <t>38,61%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>50780</t>
+          <t>50717</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>80726</t>
+          <t>82551</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3519,12 +3519,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>24,72%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>114763</t>
+          <t>113369</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>155284</t>
+          <t>153012</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>20,85%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>28,56%</t>
+          <t>28,14%</t>
         </is>
       </c>
     </row>
@@ -3582,12 +3582,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>84735</t>
+          <t>84419</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>111716</t>
+          <t>111649</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3597,12 +3597,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>40,37%</t>
+          <t>40,22%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>53,23%</t>
+          <t>53,2%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>155521</t>
+          <t>155313</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>192680</t>
+          <t>194216</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3632,12 +3632,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>46,58%</t>
+          <t>46,51%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>57,7%</t>
+          <t>58,16%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>250967</t>
+          <t>248833</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>295657</t>
+          <t>295265</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3667,12 +3667,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>46,15%</t>
+          <t>45,76%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>54,37%</t>
+          <t>54,3%</t>
         </is>
       </c>
     </row>
@@ -3695,12 +3695,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>34029</t>
+          <t>33716</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>56184</t>
+          <t>56706</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3710,12 +3710,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>26,77%</t>
+          <t>27,02%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>77526</t>
+          <t>76637</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>113005</t>
+          <t>113254</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>23,22%</t>
+          <t>22,95%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>33,84%</t>
+          <t>33,92%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>117167</t>
+          <t>117759</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>159286</t>
+          <t>159885</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>21,66%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>29,29%</t>
+          <t>29,4%</t>
         </is>
       </c>
     </row>
@@ -3925,12 +3925,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2780770</t>
+          <t>2781322</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2860304</t>
+          <t>2860798</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3940,12 +3940,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>84,87%</t>
+          <t>84,89%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>87,3%</t>
+          <t>87,31%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2542685</t>
+          <t>2541509</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>2641918</t>
+          <t>2635796</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3975,12 +3975,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>75,25%</t>
+          <t>75,21%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>78,18%</t>
+          <t>78,0%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>5353005</t>
+          <t>5346904</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>5475675</t>
+          <t>5479648</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4010,12 +4010,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>80,43%</t>
+          <t>80,34%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>82,27%</t>
+          <t>82,33%</t>
         </is>
       </c>
     </row>
@@ -4038,12 +4038,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>301996</t>
+          <t>302022</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>371394</t>
+          <t>371413</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4058,7 +4058,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4073,12 +4073,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>532418</t>
+          <t>532922</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>623494</t>
+          <t>622391</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,12 +4088,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>18,42%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4108,12 +4108,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>852849</t>
+          <t>846942</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>960674</t>
+          <t>962980</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,47%</t>
         </is>
       </c>
     </row>
@@ -4151,12 +4151,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>101039</t>
+          <t>100447</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>143626</t>
+          <t>143189</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4166,12 +4166,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4186,12 +4186,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>184782</t>
+          <t>185594</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>243533</t>
+          <t>240562</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4201,12 +4201,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>301104</t>
+          <t>297939</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>371522</t>
+          <t>369738</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4236,12 +4236,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,56%</t>
         </is>
       </c>
     </row>
@@ -4616,12 +4616,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>437546</t>
+          <t>437679</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>449604</t>
+          <t>450028</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4631,12 +4631,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>96,37%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>405206</t>
+          <t>405689</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>421331</t>
+          <t>421426</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4666,12 +4666,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>94,18%</t>
+          <t>94,3%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4686,12 +4686,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>848105</t>
+          <t>849045</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>868118</t>
+          <t>868702</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4701,12 +4701,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>96,0%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,23%</t>
         </is>
       </c>
     </row>
@@ -4729,12 +4729,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3633</t>
+          <t>3623</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15629</t>
+          <t>15518</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4749,7 +4749,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4764,12 +4764,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5389</t>
+          <t>5580</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18998</t>
+          <t>19730</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4779,12 +4779,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4799,12 +4799,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>11506</t>
+          <t>11225</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>28439</t>
+          <t>27606</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4814,12 +4814,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,12%</t>
         </is>
       </c>
     </row>
@@ -4847,7 +4847,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4345</t>
+          <t>6305</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4862,7 +4862,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4877,12 +4877,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1907</t>
+          <t>1889</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10898</t>
+          <t>11042</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4897,7 +4897,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4912,12 +4912,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1985</t>
+          <t>1962</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>12493</t>
+          <t>11763</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4932,7 +4932,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,33%</t>
         </is>
       </c>
     </row>
@@ -5072,12 +5072,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>648297</t>
+          <t>648950</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>669157</t>
+          <t>669647</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5087,12 +5087,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,35%</t>
+          <t>94,45%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5107,12 +5107,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>571134</t>
+          <t>570215</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>592945</t>
+          <t>592503</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5122,12 +5122,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,59%</t>
+          <t>93,44%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5142,12 +5142,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1227017</t>
+          <t>1227699</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1256385</t>
+          <t>1256346</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5157,7 +5157,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,58%</t>
+          <t>94,63%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -5185,12 +5185,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13280</t>
+          <t>13223</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>31974</t>
+          <t>31640</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5200,12 +5200,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5220,12 +5220,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>15315</t>
+          <t>15236</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>36494</t>
+          <t>37081</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5235,12 +5235,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5255,12 +5255,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>34019</t>
+          <t>33499</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>60040</t>
+          <t>60132</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5270,12 +5270,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,64%</t>
         </is>
       </c>
     </row>
@@ -5298,12 +5298,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1951</t>
+          <t>1887</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14269</t>
+          <t>14328</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5313,12 +5313,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5333,12 +5333,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>934</t>
+          <t>933</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8601</t>
+          <t>8200</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5353,7 +5353,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5368,12 +5368,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3851</t>
+          <t>4685</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>16301</t>
+          <t>17334</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,34%</t>
         </is>
       </c>
     </row>
@@ -5528,12 +5528,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>628204</t>
+          <t>626894</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>651837</t>
+          <t>652401</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>92,39%</t>
+          <t>92,2%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>95,95%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5563,12 +5563,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>617332</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>649766</t>
+          <t>651720</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>86,84%</t>
+          <t>86,97%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>91,41%</t>
+          <t>91,68%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5598,12 +5598,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1254259</t>
+          <t>1254515</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1297477</t>
+          <t>1295699</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>90,18%</t>
+          <t>90,2%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>93,29%</t>
+          <t>93,16%</t>
         </is>
       </c>
     </row>
@@ -5641,12 +5641,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>21155</t>
+          <t>21376</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>42252</t>
+          <t>44732</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5676,12 +5676,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>41604</t>
+          <t>40351</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>69640</t>
+          <t>69909</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5711,12 +5711,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>67167</t>
+          <t>68580</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>105018</t>
+          <t>104314</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,5%</t>
         </is>
       </c>
     </row>
@@ -5754,12 +5754,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3181</t>
+          <t>3699</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>17141</t>
+          <t>16769</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5769,12 +5769,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5789,12 +5789,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>12804</t>
+          <t>12884</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>33309</t>
+          <t>32473</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5824,12 +5824,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>19953</t>
+          <t>18945</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>43774</t>
+          <t>43119</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,1%</t>
         </is>
       </c>
     </row>
@@ -5984,12 +5984,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>532829</t>
+          <t>531948</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>564626</t>
+          <t>563810</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>86,69%</t>
+          <t>86,55%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>91,87%</t>
+          <t>91,73%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6019,12 +6019,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>493080</t>
+          <t>492265</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>530900</t>
+          <t>531839</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>80,02%</t>
+          <t>79,89%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>86,16%</t>
+          <t>86,31%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6054,12 +6054,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1037771</t>
+          <t>1039168</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1085470</t>
+          <t>1086680</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>84,32%</t>
+          <t>84,43%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>88,19%</t>
+          <t>88,29%</t>
         </is>
       </c>
     </row>
@@ -6097,12 +6097,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>33791</t>
+          <t>34763</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>61776</t>
+          <t>62935</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6132,12 +6132,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>56087</t>
+          <t>55338</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>88248</t>
+          <t>88974</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6167,12 +6167,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>96388</t>
+          <t>98600</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>139434</t>
+          <t>141129</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,47%</t>
         </is>
       </c>
     </row>
@@ -6210,12 +6210,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>11323</t>
+          <t>11218</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>30670</t>
+          <t>28619</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6245,12 +6245,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>20269</t>
+          <t>20721</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>41692</t>
+          <t>44101</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6280,12 +6280,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>37077</t>
+          <t>37524</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>64757</t>
+          <t>66979</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6295,12 +6295,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,44%</t>
         </is>
       </c>
     </row>
@@ -6440,12 +6440,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>321703</t>
+          <t>322408</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>356859</t>
+          <t>356428</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6455,12 +6455,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>75,27%</t>
+          <t>75,43%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>83,49%</t>
+          <t>83,39%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6475,12 +6475,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>262676</t>
+          <t>263850</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>304024</t>
+          <t>304434</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>58,66%</t>
+          <t>58,92%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>67,89%</t>
+          <t>67,98%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6510,12 +6510,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>595163</t>
+          <t>594992</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>652701</t>
+          <t>650866</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6525,12 +6525,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>68,0%</t>
+          <t>67,98%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>74,58%</t>
+          <t>74,37%</t>
         </is>
       </c>
     </row>
@@ -6553,12 +6553,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>47458</t>
+          <t>47273</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>78533</t>
+          <t>76829</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>17,98%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6588,12 +6588,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>104132</t>
+          <t>102266</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>142139</t>
+          <t>141673</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>22,84%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>31,74%</t>
+          <t>31,64%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6623,12 +6623,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>158256</t>
+          <t>157404</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>207852</t>
+          <t>206530</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6638,12 +6638,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>17,98%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>23,75%</t>
+          <t>23,6%</t>
         </is>
       </c>
     </row>
@@ -6666,12 +6666,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>17984</t>
+          <t>17618</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>38667</t>
+          <t>38658</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6681,12 +6681,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6701,12 +6701,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>31310</t>
+          <t>31218</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>57391</t>
+          <t>55871</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6716,12 +6716,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6736,12 +6736,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>53555</t>
+          <t>52190</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>87492</t>
+          <t>85745</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6751,12 +6751,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>9,8%</t>
         </is>
       </c>
     </row>
@@ -6896,12 +6896,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>160787</t>
+          <t>161997</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>198836</t>
+          <t>197737</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6911,12 +6911,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>51,9%</t>
+          <t>52,29%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>64,18%</t>
+          <t>63,83%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6931,12 +6931,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>126088</t>
+          <t>127008</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>164603</t>
+          <t>165168</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>35,62%</t>
+          <t>35,88%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>46,5%</t>
+          <t>46,66%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6966,12 +6966,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>300604</t>
+          <t>298969</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>352130</t>
+          <t>352649</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6981,12 +6981,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>45,29%</t>
+          <t>45,04%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>53,05%</t>
+          <t>53,13%</t>
         </is>
       </c>
     </row>
@@ -7009,12 +7009,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>71917</t>
+          <t>72363</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>106029</t>
+          <t>105260</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7024,12 +7024,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>23,22%</t>
+          <t>23,36%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>34,23%</t>
+          <t>33,98%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7044,12 +7044,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>116020</t>
+          <t>114458</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>152819</t>
+          <t>150829</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>32,77%</t>
+          <t>32,33%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>43,17%</t>
+          <t>42,61%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7079,12 +7079,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>195824</t>
+          <t>194558</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>247441</t>
+          <t>247322</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7094,12 +7094,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>29,5%</t>
+          <t>29,31%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>37,28%</t>
+          <t>37,26%</t>
         </is>
       </c>
     </row>
@@ -7122,12 +7122,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>29277</t>
+          <t>28047</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>53746</t>
+          <t>54231</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>17,51%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7157,12 +7157,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>61677</t>
+          <t>60567</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>93254</t>
+          <t>92960</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>17,11%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>26,34%</t>
+          <t>26,26%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7192,12 +7192,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>96900</t>
+          <t>98302</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>137664</t>
+          <t>138171</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7207,12 +7207,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>20,74%</t>
+          <t>20,82%</t>
         </is>
       </c>
     </row>
@@ -7352,12 +7352,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>57869</t>
+          <t>57949</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>89973</t>
+          <t>88035</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7367,12 +7367,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>23,16%</t>
+          <t>23,19%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>36,01%</t>
+          <t>35,24%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7387,12 +7387,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>50603</t>
+          <t>49338</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>80182</t>
+          <t>80857</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>20,85%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7422,12 +7422,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>116202</t>
+          <t>116797</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>159068</t>
+          <t>160656</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7437,12 +7437,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>18,31%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>24,94%</t>
+          <t>25,19%</t>
         </is>
       </c>
     </row>
@@ -7465,12 +7465,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>86924</t>
+          <t>87832</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>119810</t>
+          <t>119796</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7480,7 +7480,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>34,79%</t>
+          <t>35,15%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -7500,12 +7500,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>135043</t>
+          <t>134416</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>173924</t>
+          <t>175335</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7515,12 +7515,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>34,81%</t>
+          <t>34,65%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>44,84%</t>
+          <t>45,2%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>229187</t>
+          <t>230675</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>283117</t>
+          <t>282451</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7550,12 +7550,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>35,94%</t>
+          <t>36,17%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>44,39%</t>
+          <t>44,29%</t>
         </is>
       </c>
     </row>
@@ -7578,12 +7578,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>57934</t>
+          <t>58875</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>90096</t>
+          <t>92050</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7593,12 +7593,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>23,19%</t>
+          <t>23,56%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>36,06%</t>
+          <t>36,84%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7613,12 +7613,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>147869</t>
+          <t>150493</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>188529</t>
+          <t>191265</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7628,12 +7628,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>38,12%</t>
+          <t>38,8%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>48,6%</t>
+          <t>49,31%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7648,12 +7648,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>216768</t>
+          <t>217253</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>271108</t>
+          <t>268886</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7663,12 +7663,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>33,99%</t>
+          <t>34,07%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>42,51%</t>
+          <t>42,16%</t>
         </is>
       </c>
     </row>
@@ -7808,12 +7808,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2847280</t>
+          <t>2843856</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2935148</t>
+          <t>2932563</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7823,12 +7823,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>83,18%</t>
+          <t>83,08%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>85,75%</t>
+          <t>85,68%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7843,12 +7843,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2588235</t>
+          <t>2586883</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>2693905</t>
+          <t>2691041</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7858,12 +7858,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>72,76%</t>
+          <t>72,72%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>75,73%</t>
+          <t>75,65%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7878,12 +7878,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>5464932</t>
+          <t>5453822</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>5599342</t>
+          <t>5594276</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7893,12 +7893,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>78,29%</t>
+          <t>78,13%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>80,22%</t>
+          <t>80,15%</t>
         </is>
       </c>
     </row>
@@ -7921,12 +7921,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>321248</t>
+          <t>325187</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>396264</t>
+          <t>398817</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -7936,12 +7936,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -7956,12 +7956,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>529916</t>
+          <t>524701</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>615914</t>
+          <t>612079</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -7971,12 +7971,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -7991,12 +7991,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>873010</t>
+          <t>868670</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>986556</t>
+          <t>986509</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -8006,7 +8006,7 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
@@ -8034,12 +8034,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>147007</t>
+          <t>148336</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>202521</t>
+          <t>204958</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8049,12 +8049,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8069,12 +8069,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>313393</t>
+          <t>310790</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>385717</t>
+          <t>383365</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8104,12 +8104,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>482134</t>
+          <t>476902</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>568634</t>
+          <t>566675</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8119,12 +8119,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,12%</t>
         </is>
       </c>
     </row>
@@ -8499,12 +8499,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>410492</t>
+          <t>409745</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>418498</t>
+          <t>418494</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8514,7 +8514,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>373406</t>
+          <t>373300</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>388110</t>
+          <t>388008</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8549,12 +8549,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>94,35%</t>
+          <t>94,33%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>788466</t>
+          <t>786775</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>805467</t>
+          <t>804610</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8584,12 +8584,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>96,51%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,7%</t>
         </is>
       </c>
     </row>
@@ -8612,12 +8612,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>965</t>
+          <t>969</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8971</t>
+          <t>9718</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8632,7 +8632,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8647,12 +8647,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7340</t>
+          <t>7551</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>21162</t>
+          <t>21434</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8662,12 +8662,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8682,12 +8682,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>9130</t>
+          <t>10084</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>25157</t>
+          <t>26880</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8697,12 +8697,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,3%</t>
         </is>
       </c>
     </row>
@@ -8765,7 +8765,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5788</t>
+          <t>5296</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8780,7 +8780,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8800,7 +8800,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>5802</t>
+          <t>4129</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8815,7 +8815,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,51%</t>
         </is>
       </c>
     </row>
@@ -8955,12 +8955,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>565378</t>
+          <t>563678</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>581612</t>
+          <t>581087</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8970,12 +8970,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>95,46%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8990,12 +8990,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>527103</t>
+          <t>526761</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>547894</t>
+          <t>547094</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9005,12 +9005,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,53%</t>
+          <t>93,47%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9025,12 +9025,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1098381</t>
+          <t>1098780</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1124255</t>
+          <t>1124557</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9040,12 +9040,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,18%</t>
+          <t>95,21%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,45%</t>
         </is>
       </c>
     </row>
@@ -9068,12 +9068,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7462</t>
+          <t>8207</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>22970</t>
+          <t>24652</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9083,12 +9083,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -9103,12 +9103,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>8279</t>
+          <t>8648</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>24341</t>
+          <t>24503</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9118,12 +9118,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -9138,12 +9138,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>20193</t>
+          <t>19953</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>42228</t>
+          <t>41686</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9153,12 +9153,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,61%</t>
         </is>
       </c>
     </row>
@@ -9186,7 +9186,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7336</t>
+          <t>6044</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9201,7 +9201,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9216,12 +9216,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4634</t>
+          <t>4624</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>17820</t>
+          <t>17697</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9236,7 +9236,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9251,12 +9251,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6134</t>
+          <t>5880</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>20237</t>
+          <t>19591</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9266,12 +9266,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,7%</t>
         </is>
       </c>
     </row>
@@ -9411,12 +9411,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>619785</t>
+          <t>619775</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>643067</t>
+          <t>644069</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9431,7 +9431,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9446,12 +9446,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>598275</t>
+          <t>600494</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>625437</t>
+          <t>625756</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9461,12 +9461,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>90,46%</t>
+          <t>90,79%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>94,56%</t>
+          <t>94,61%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9481,12 +9481,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1227670</t>
+          <t>1224748</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1263642</t>
+          <t>1262227</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9496,12 +9496,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>92,27%</t>
+          <t>92,05%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>94,87%</t>
         </is>
       </c>
     </row>
@@ -9524,12 +9524,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>20016</t>
+          <t>19466</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>41602</t>
+          <t>41582</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9539,12 +9539,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9559,12 +9559,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>29310</t>
+          <t>29290</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>55450</t>
+          <t>54076</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9579,7 +9579,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9594,12 +9594,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>53825</t>
+          <t>54507</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>87435</t>
+          <t>88810</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9609,12 +9609,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,68%</t>
         </is>
       </c>
     </row>
@@ -9637,12 +9637,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3030</t>
+          <t>2868</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>14615</t>
+          <t>13393</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9652,12 +9652,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9672,12 +9672,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2823</t>
+          <t>2858</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>13424</t>
+          <t>13871</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9692,7 +9692,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9707,12 +9707,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>8032</t>
+          <t>7587</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>22895</t>
+          <t>22708</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9722,12 +9722,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,71%</t>
         </is>
       </c>
     </row>
@@ -9867,12 +9867,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>548123</t>
+          <t>549532</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>583891</t>
+          <t>583168</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>84,84%</t>
+          <t>85,06%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>90,38%</t>
+          <t>90,27%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>535051</t>
+          <t>534077</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>570699</t>
+          <t>571769</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>82,43%</t>
+          <t>82,28%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>87,92%</t>
+          <t>88,09%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9937,12 +9937,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1097337</t>
+          <t>1095232</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1146808</t>
+          <t>1145636</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9952,12 +9952,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>84,73%</t>
+          <t>84,57%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>88,55%</t>
+          <t>88,46%</t>
         </is>
       </c>
     </row>
@@ -9980,12 +9980,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>34118</t>
+          <t>32822</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>61686</t>
+          <t>59117</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9995,12 +9995,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10015,12 +10015,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>42195</t>
+          <t>42729</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>70183</t>
+          <t>71511</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10030,12 +10030,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10050,12 +10050,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>82471</t>
+          <t>81945</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>121506</t>
+          <t>122724</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10065,12 +10065,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,48%</t>
         </is>
       </c>
     </row>
@@ -10093,12 +10093,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>22167</t>
+          <t>21917</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>45086</t>
+          <t>45128</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10108,12 +10108,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -10128,12 +10128,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>29746</t>
+          <t>28963</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>52970</t>
+          <t>54863</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10143,12 +10143,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -10163,12 +10163,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>56683</t>
+          <t>56270</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>90983</t>
+          <t>92680</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10178,12 +10178,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,16%</t>
         </is>
       </c>
     </row>
@@ -10323,12 +10323,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>359566</t>
+          <t>361546</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>398587</t>
+          <t>399035</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10338,12 +10338,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>75,24%</t>
+          <t>75,65%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>83,4%</t>
+          <t>83,49%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10358,12 +10358,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>314819</t>
+          <t>316719</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>358508</t>
+          <t>358423</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>63,36%</t>
+          <t>63,75%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>72,16%</t>
+          <t>72,14%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10393,12 +10393,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>688323</t>
+          <t>690458</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>749687</t>
+          <t>749639</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10408,12 +10408,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>70,61%</t>
+          <t>70,83%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>76,91%</t>
+          <t>76,9%</t>
         </is>
       </c>
     </row>
@@ -10436,12 +10436,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>61057</t>
+          <t>60638</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>96050</t>
+          <t>94761</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10451,12 +10451,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>19,83%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10471,12 +10471,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>81691</t>
+          <t>82179</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>117152</t>
+          <t>118081</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10486,12 +10486,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>23,58%</t>
+          <t>23,77%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10506,12 +10506,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>150861</t>
+          <t>150063</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>202770</t>
+          <t>201141</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10521,12 +10521,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>15,39%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>20,8%</t>
+          <t>20,63%</t>
         </is>
       </c>
     </row>
@@ -10549,12 +10549,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>12371</t>
+          <t>11960</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>32023</t>
+          <t>31954</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10564,12 +10564,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10584,12 +10584,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>45986</t>
+          <t>46320</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>75885</t>
+          <t>74757</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10599,12 +10599,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10619,12 +10619,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>63312</t>
+          <t>63257</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>101997</t>
+          <t>100133</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10634,12 +10634,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,27%</t>
         </is>
       </c>
     </row>
@@ -10779,12 +10779,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>202645</t>
+          <t>202287</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>236985</t>
+          <t>236077</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>60,61%</t>
+          <t>60,51%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>70,88%</t>
+          <t>70,61%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10814,12 +10814,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>177604</t>
+          <t>177616</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>216598</t>
+          <t>214826</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10829,12 +10829,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>47,01%</t>
+          <t>47,02%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>57,34%</t>
+          <t>56,87%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10849,12 +10849,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>389136</t>
+          <t>392361</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>442334</t>
+          <t>442063</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10864,12 +10864,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>54,65%</t>
+          <t>55,1%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>62,12%</t>
+          <t>62,08%</t>
         </is>
       </c>
     </row>
@@ -10892,12 +10892,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>60538</t>
+          <t>61901</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>92210</t>
+          <t>92276</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10907,12 +10907,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>18,52%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>27,58%</t>
+          <t>27,6%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10927,12 +10927,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>103638</t>
+          <t>105392</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>140138</t>
+          <t>141734</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10942,12 +10942,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>27,43%</t>
+          <t>27,9%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>37,1%</t>
+          <t>37,52%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10962,12 +10962,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>173794</t>
+          <t>174654</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>224386</t>
+          <t>224333</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10977,12 +10977,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>24,41%</t>
+          <t>24,53%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>31,51%</t>
+          <t>31,5%</t>
         </is>
       </c>
     </row>
@@ -11005,12 +11005,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>28403</t>
+          <t>28165</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>53253</t>
+          <t>51170</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -11020,12 +11020,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>15,31%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -11040,12 +11040,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>45460</t>
+          <t>44179</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>74135</t>
+          <t>71463</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -11055,12 +11055,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>18,92%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -11075,12 +11075,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>79898</t>
+          <t>80446</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>115884</t>
+          <t>116136</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -11090,12 +11090,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>16,31%</t>
         </is>
       </c>
     </row>
@@ -11235,12 +11235,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>96221</t>
+          <t>94847</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>122476</t>
+          <t>125219</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -11250,12 +11250,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>37,44%</t>
+          <t>36,91%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>47,66%</t>
+          <t>48,72%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -11270,12 +11270,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>92819</t>
+          <t>92850</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>136338</t>
+          <t>133785</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -11285,12 +11285,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>23,19%</t>
+          <t>23,2%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>34,07%</t>
+          <t>33,43%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -11305,12 +11305,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>197096</t>
+          <t>195331</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>246266</t>
+          <t>246563</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -11320,12 +11320,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>29,99%</t>
+          <t>29,72%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>37,47%</t>
+          <t>37,52%</t>
         </is>
       </c>
     </row>
@@ -11348,12 +11348,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>80992</t>
+          <t>81512</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>108936</t>
+          <t>110446</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -11363,12 +11363,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>31,51%</t>
+          <t>31,72%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>42,39%</t>
+          <t>42,98%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -11383,12 +11383,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>124037</t>
+          <t>127308</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>167474</t>
+          <t>172563</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -11398,12 +11398,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>31,0%</t>
+          <t>31,81%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>41,85%</t>
+          <t>43,12%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -11418,12 +11418,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>220327</t>
+          <t>220514</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>269531</t>
+          <t>270991</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -11433,12 +11433,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>33,53%</t>
+          <t>33,56%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>41,01%</t>
+          <t>41,24%</t>
         </is>
       </c>
     </row>
@@ -11461,12 +11461,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>41842</t>
+          <t>41550</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>65841</t>
+          <t>65927</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -11476,12 +11476,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>16,17%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>25,62%</t>
+          <t>25,65%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11496,12 +11496,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>120383</t>
+          <t>119218</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>162224</t>
+          <t>162492</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11511,12 +11511,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>30,08%</t>
+          <t>29,79%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>40,54%</t>
+          <t>40,61%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11531,12 +11531,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>168014</t>
+          <t>168592</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>217439</t>
+          <t>218555</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11546,12 +11546,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>25,57%</t>
+          <t>25,65%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>33,09%</t>
+          <t>33,26%</t>
         </is>
       </c>
     </row>
@@ -11691,12 +11691,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2857004</t>
+          <t>2861021</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2944841</t>
+          <t>2940475</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11706,12 +11706,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>84,17%</t>
+          <t>84,29%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>86,76%</t>
+          <t>86,63%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11726,12 +11726,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2682849</t>
+          <t>2677664</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>2784478</t>
+          <t>2784706</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11741,7 +11741,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>75,69%</t>
+          <t>75,54%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -11761,12 +11761,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>5573243</t>
+          <t>5568949</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>5708616</t>
+          <t>5705241</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11776,12 +11776,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>80,32%</t>
+          <t>80,26%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>82,27%</t>
+          <t>82,22%</t>
         </is>
       </c>
     </row>
@@ -11804,12 +11804,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>303815</t>
+          <t>304102</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>375847</t>
+          <t>375660</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -11819,7 +11819,7 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
@@ -11839,12 +11839,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>452050</t>
+          <t>451158</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>542378</t>
+          <t>535091</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -11854,12 +11854,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>15,1%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -11874,12 +11874,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>777516</t>
+          <t>774998</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>884242</t>
+          <t>887207</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -11889,12 +11889,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>12,79%</t>
         </is>
       </c>
     </row>
@@ -11917,12 +11917,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>131610</t>
+          <t>129325</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>179052</t>
+          <t>176594</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -11932,12 +11932,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -11952,12 +11952,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>279409</t>
+          <t>281066</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>355076</t>
+          <t>356239</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -11967,12 +11967,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -11987,12 +11987,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>426191</t>
+          <t>425839</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>511439</t>
+          <t>515283</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -12007,7 +12007,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,43%</t>
         </is>
       </c>
     </row>
@@ -12377,27 +12377,27 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>394453</t>
+          <t>402531</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>378638</t>
+          <t>389955</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>94,66%</t>
+          <t>95,63%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -12412,32 +12412,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>306426</t>
+          <t>353017</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>295726</t>
+          <t>341699</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>311402</t>
+          <t>359649</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,38%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>94,42%</t>
+          <t>94,26%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,21%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -12447,32 +12447,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>700879</t>
+          <t>755548</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>684782</t>
+          <t>739604</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>707982</t>
+          <t>764205</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>96,01%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,21%</t>
         </is>
       </c>
     </row>
@@ -12490,7 +12490,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5534</t>
+          <t>5262</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -12500,12 +12500,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>21349</t>
+          <t>17838</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -12515,7 +12515,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -12525,67 +12525,67 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5153</t>
+          <t>7463</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1162</t>
+          <t>1729</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>15368</t>
+          <t>18000</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
+          <t>2,06%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>0,48%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>4,97%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>12725</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>4700</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>28329</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
           <t>1,65%</t>
         </is>
       </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>4,91%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>10687</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>3945</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>26812</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>1,5%</t>
-        </is>
-      </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,68%</t>
         </is>
       </c>
     </row>
@@ -12638,7 +12638,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1621</t>
+          <t>2032</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -12648,12 +12648,12 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8892</t>
+          <t>10175</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
@@ -12663,7 +12663,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -12673,7 +12673,7 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1621</t>
+          <t>2032</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
@@ -12683,12 +12683,12 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>9864</t>
+          <t>11862</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
@@ -12698,7 +12698,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,54%</t>
         </is>
       </c>
     </row>
@@ -12716,17 +12716,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -12751,17 +12751,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -12786,17 +12786,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -12833,32 +12833,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>409098</t>
+          <t>460946</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>397370</t>
+          <t>448683</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>415793</t>
+          <t>468399</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>96,66%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>94,09%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -12868,32 +12868,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>505614</t>
+          <t>494396</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>498328</t>
+          <t>487366</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>509649</t>
+          <t>498622</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,54%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,14%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,38%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -12903,32 +12903,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>914712</t>
+          <t>955341</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>900429</t>
+          <t>943077</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>922882</t>
+          <t>964304</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,62%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>96,37%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,54%</t>
         </is>
       </c>
     </row>
@@ -12946,32 +12946,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9726</t>
+          <t>10780</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3957</t>
+          <t>4982</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>20427</t>
+          <t>21581</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -12981,32 +12981,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5565</t>
+          <t>6390</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1981</t>
+          <t>2800</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>12398</t>
+          <t>12980</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -13016,32 +13016,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>15290</t>
+          <t>17170</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>8194</t>
+          <t>9325</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>27613</t>
+          <t>29409</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,01%</t>
         </is>
       </c>
     </row>
@@ -13059,32 +13059,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>4723</t>
+          <t>5165</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1186</t>
+          <t>1287</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11485</t>
+          <t>12641</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -13094,7 +13094,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>914</t>
+          <t>947</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -13104,12 +13104,12 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5367</t>
+          <t>5376</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -13119,7 +13119,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -13129,32 +13129,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>5638</t>
+          <t>6112</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2027</t>
+          <t>2210</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>12939</t>
+          <t>13206</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,35%</t>
         </is>
       </c>
     </row>
@@ -13172,17 +13172,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -13207,17 +13207,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>512093</t>
+          <t>501733</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>512093</t>
+          <t>501733</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>512093</t>
+          <t>501733</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -13242,17 +13242,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>935640</t>
+          <t>978623</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>935640</t>
+          <t>978623</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>935640</t>
+          <t>978623</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -13289,32 +13289,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>506362</t>
+          <t>590447</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>493445</t>
+          <t>577972</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>516139</t>
+          <t>600507</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>94,41%</t>
+          <t>95,11%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>92,0%</t>
+          <t>93,1%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>96,23%</t>
+          <t>96,73%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -13324,32 +13324,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>552502</t>
+          <t>577634</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>540490</t>
+          <t>565648</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>563963</t>
+          <t>587141</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>93,41%</t>
+          <t>92,78%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>91,38%</t>
+          <t>90,86%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>94,31%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -13359,32 +13359,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1058864</t>
+          <t>1168081</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1041963</t>
+          <t>1149675</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1073701</t>
+          <t>1182422</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>93,89%</t>
+          <t>93,94%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>92,39%</t>
+          <t>92,46%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,1%</t>
         </is>
       </c>
     </row>
@@ -13402,32 +13402,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>25231</t>
+          <t>25443</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>16440</t>
+          <t>16608</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>37115</t>
+          <t>37423</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -13437,32 +13437,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>28869</t>
+          <t>34544</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>19642</t>
+          <t>25252</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>39105</t>
+          <t>44848</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -13472,32 +13472,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>54100</t>
+          <t>59987</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>41120</t>
+          <t>45673</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>68942</t>
+          <t>74685</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,01%</t>
         </is>
       </c>
     </row>
@@ -13515,32 +13515,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>4745</t>
+          <t>4947</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1297</t>
+          <t>1355</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>12067</t>
+          <t>12820</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -13550,22 +13550,22 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>10086</t>
+          <t>10378</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>5663</t>
+          <t>5963</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>16614</t>
+          <t>16371</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
@@ -13575,7 +13575,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -13585,32 +13585,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>14831</t>
+          <t>15324</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>8844</t>
+          <t>8836</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>23019</t>
+          <t>24050</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>1,93%</t>
         </is>
       </c>
     </row>
@@ -13628,17 +13628,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -13663,17 +13663,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>591457</t>
+          <t>622556</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>591457</t>
+          <t>622556</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>591457</t>
+          <t>622556</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -13698,17 +13698,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1127795</t>
+          <t>1243393</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1127795</t>
+          <t>1243393</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1127795</t>
+          <t>1243393</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -13745,32 +13745,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>570965</t>
+          <t>620808</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>240454</t>
+          <t>598710</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>795158</t>
+          <t>636539</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>64,31%</t>
+          <t>88,61%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>27,08%</t>
+          <t>85,45%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>89,57%</t>
+          <t>90,85%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -13780,32 +13780,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>624834</t>
+          <t>646372</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>605902</t>
+          <t>631978</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>640813</t>
+          <t>659240</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>87,65%</t>
+          <t>87,72%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>84,99%</t>
+          <t>85,76%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>89,89%</t>
+          <t>89,46%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -13815,32 +13815,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1195799</t>
+          <t>1267181</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>796784</t>
+          <t>1242529</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1420092</t>
+          <t>1288083</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>74,71%</t>
+          <t>88,15%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>49,78%</t>
+          <t>86,44%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>88,72%</t>
+          <t>89,61%</t>
         </is>
       </c>
     </row>
@@ -13858,32 +13858,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>289638</t>
+          <t>50651</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>56955</t>
+          <t>36770</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>636801</t>
+          <t>66519</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>32,62%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>71,73%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -13893,32 +13893,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>64860</t>
+          <t>66623</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>51087</t>
+          <t>55236</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>83861</t>
+          <t>80986</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -13928,32 +13928,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>354497</t>
+          <t>117274</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>122627</t>
+          <t>98376</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>771104</t>
+          <t>136421</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>48,17%</t>
+          <t>9,49%</t>
         </is>
       </c>
     </row>
@@ -13971,32 +13971,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>27184</t>
+          <t>29158</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>11288</t>
+          <t>19721</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>44075</t>
+          <t>43132</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -14006,32 +14006,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>23187</t>
+          <t>23892</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>15770</t>
+          <t>17422</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>31620</t>
+          <t>32417</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -14041,32 +14041,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>50371</t>
+          <t>53049</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>30311</t>
+          <t>39980</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>69180</t>
+          <t>68506</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,77%</t>
         </is>
       </c>
     </row>
@@ -14084,17 +14084,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -14119,17 +14119,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -14154,17 +14154,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -14201,32 +14201,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>440694</t>
+          <t>483148</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>422475</t>
+          <t>462548</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>459093</t>
+          <t>502263</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>78,52%</t>
+          <t>79,29%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>75,28%</t>
+          <t>75,91%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>81,8%</t>
+          <t>82,43%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -14236,32 +14236,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>408751</t>
+          <t>452189</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>394177</t>
+          <t>435806</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>423653</t>
+          <t>467888</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>74,6%</t>
+          <t>74,27%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>71,94%</t>
+          <t>71,58%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>77,32%</t>
+          <t>76,85%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -14271,27 +14271,27 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>849445</t>
+          <t>935337</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>826053</t>
+          <t>906049</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>872723</t>
+          <t>958450</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>76,59%</t>
+          <t>76,78%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>74,48%</t>
+          <t>74,38%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -14314,32 +14314,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>89099</t>
+          <t>92839</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>72763</t>
+          <t>76333</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>106159</t>
+          <t>111318</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -14349,32 +14349,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>100066</t>
+          <t>112083</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>86900</t>
+          <t>97551</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>113312</t>
+          <t>126263</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>18,41%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>20,68%</t>
+          <t>20,74%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -14384,32 +14384,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>189165</t>
+          <t>204923</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>169124</t>
+          <t>182756</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>210858</t>
+          <t>228723</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>16,82%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>19,01%</t>
+          <t>18,78%</t>
         </is>
       </c>
     </row>
@@ -14427,32 +14427,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>31441</t>
+          <t>33360</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>22379</t>
+          <t>22491</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>43088</t>
+          <t>45200</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -14462,32 +14462,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>39088</t>
+          <t>44583</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>30515</t>
+          <t>35427</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>48078</t>
+          <t>54876</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -14497,32 +14497,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>70529</t>
+          <t>77943</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>57384</t>
+          <t>64488</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>84904</t>
+          <t>94496</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,76%</t>
         </is>
       </c>
     </row>
@@ -14540,17 +14540,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -14575,17 +14575,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>547905</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>547905</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>547905</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -14610,17 +14610,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1109139</t>
+          <t>1218202</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1109139</t>
+          <t>1218202</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1109139</t>
+          <t>1218202</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -14657,32 +14657,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>273832</t>
+          <t>303556</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>260068</t>
+          <t>288464</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>285936</t>
+          <t>318237</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>74,53%</t>
+          <t>74,73%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>70,78%</t>
+          <t>71,01%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>77,82%</t>
+          <t>78,34%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -14692,32 +14692,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>444649</t>
+          <t>258016</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>355698</t>
+          <t>243644</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>535618</t>
+          <t>273499</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>73,09%</t>
+          <t>58,75%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>58,47%</t>
+          <t>55,48%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>88,04%</t>
+          <t>62,28%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -14727,32 +14727,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>718481</t>
+          <t>561572</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>642448</t>
+          <t>540237</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>842441</t>
+          <t>582280</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>73,63%</t>
+          <t>66,43%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>65,84%</t>
+          <t>63,91%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>86,33%</t>
+          <t>68,88%</t>
         </is>
       </c>
     </row>
@@ -14770,32 +14770,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>66445</t>
+          <t>73696</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>55137</t>
+          <t>60855</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>78876</t>
+          <t>88654</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>18,14%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>14,98%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -14805,32 +14805,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>120345</t>
+          <t>132056</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>52935</t>
+          <t>118346</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>187492</t>
+          <t>147006</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>19,78%</t>
+          <t>30,07%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>26,95%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>30,82%</t>
+          <t>33,47%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -14840,32 +14840,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>186790</t>
+          <t>205753</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>94106</t>
+          <t>186220</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>241830</t>
+          <t>225307</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>24,34%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>22,03%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>24,78%</t>
+          <t>26,65%</t>
         </is>
       </c>
     </row>
@@ -14883,32 +14883,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>27141</t>
+          <t>28953</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>19664</t>
+          <t>20817</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>35795</t>
+          <t>38078</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -14918,32 +14918,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>43374</t>
+          <t>49093</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>19067</t>
+          <t>40094</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>69612</t>
+          <t>59855</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -14953,32 +14953,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>70515</t>
+          <t>78047</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>37246</t>
+          <t>64935</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>94541</t>
+          <t>91638</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>10,84%</t>
         </is>
       </c>
     </row>
@@ -14996,17 +14996,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>367418</t>
+          <t>406205</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>367418</t>
+          <t>406205</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>367418</t>
+          <t>406205</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -15031,17 +15031,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -15066,17 +15066,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>975786</t>
+          <t>845372</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>975786</t>
+          <t>845372</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>975786</t>
+          <t>845372</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -15113,32 +15113,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>129006</t>
+          <t>141381</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>116065</t>
+          <t>127508</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>142426</t>
+          <t>157954</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>45,62%</t>
+          <t>45,58%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>41,05%</t>
+          <t>41,11%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>50,37%</t>
+          <t>50,92%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -15148,32 +15148,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>93984</t>
+          <t>104283</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>83454</t>
+          <t>91827</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>107239</t>
+          <t>118635</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>22,47%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>19,79%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>25,57%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -15183,32 +15183,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>222990</t>
+          <t>245665</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>204749</t>
+          <t>225358</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>241248</t>
+          <t>267320</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>31,5%</t>
+          <t>31,73%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>28,92%</t>
+          <t>29,11%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>34,07%</t>
+          <t>34,53%</t>
         </is>
       </c>
     </row>
@@ -15226,32 +15226,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>97949</t>
+          <t>108540</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>86036</t>
+          <t>94198</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>112628</t>
+          <t>122667</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>34,64%</t>
+          <t>34,99%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>30,43%</t>
+          <t>30,37%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>39,83%</t>
+          <t>39,54%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -15261,32 +15261,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>172784</t>
+          <t>184784</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>158257</t>
+          <t>170580</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>186752</t>
+          <t>199536</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>40,63%</t>
+          <t>39,82%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>37,21%</t>
+          <t>36,76%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>43,91%</t>
+          <t>43,0%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -15296,32 +15296,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>270733</t>
+          <t>293324</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>251015</t>
+          <t>273465</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>290356</t>
+          <t>314485</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>38,24%</t>
+          <t>37,89%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>35,45%</t>
+          <t>35,32%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>41,01%</t>
+          <t>40,62%</t>
         </is>
       </c>
     </row>
@@ -15339,32 +15339,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>55804</t>
+          <t>60277</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>46364</t>
+          <t>49287</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>67530</t>
+          <t>72222</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>19,43%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>23,88%</t>
+          <t>23,28%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -15374,32 +15374,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>158490</t>
+          <t>174965</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>143847</t>
+          <t>158906</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>172441</t>
+          <t>191159</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>37,27%</t>
+          <t>37,71%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>33,83%</t>
+          <t>34,24%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>40,55%</t>
+          <t>41,2%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -15409,32 +15409,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>214294</t>
+          <t>235242</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>196223</t>
+          <t>216863</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>232499</t>
+          <t>254391</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>30,27%</t>
+          <t>30,38%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>27,71%</t>
+          <t>28,01%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>32,84%</t>
+          <t>32,86%</t>
         </is>
       </c>
     </row>
@@ -15452,17 +15452,17 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -15487,17 +15487,17 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>425258</t>
+          <t>464033</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>425258</t>
+          <t>464033</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>425258</t>
+          <t>464033</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -15522,17 +15522,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>708017</t>
+          <t>774231</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>708017</t>
+          <t>774231</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>708017</t>
+          <t>774231</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -15569,32 +15569,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>2724411</t>
+          <t>3002818</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2136835</t>
+          <t>2958846</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2946868</t>
+          <t>3038767</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>78,76%</t>
+          <t>85,02%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>61,77%</t>
+          <t>83,78%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>85,19%</t>
+          <t>86,04%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -15604,32 +15604,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>2936759</t>
+          <t>2885907</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2867724</t>
+          <t>2844887</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>3085463</t>
+          <t>2925015</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>79,13%</t>
+          <t>77,25%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>77,27%</t>
+          <t>76,15%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>83,14%</t>
+          <t>78,3%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -15639,32 +15639,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>5661170</t>
+          <t>5888725</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>5087714</t>
+          <t>5826941</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>5904243</t>
+          <t>5943712</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>78,95%</t>
+          <t>81,03%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>70,96%</t>
+          <t>80,18%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>82,34%</t>
+          <t>81,78%</t>
         </is>
       </c>
     </row>
@@ -15682,32 +15682,32 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>583621</t>
+          <t>367211</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>353796</t>
+          <t>336582</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>1210510</t>
+          <t>405917</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>35,0%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -15717,32 +15717,32 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>497642</t>
+          <t>543945</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>405299</t>
+          <t>514005</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>547031</t>
+          <t>578659</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -15752,32 +15752,32 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>1081262</t>
+          <t>911156</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>836345</t>
+          <t>865238</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>1789488</t>
+          <t>959301</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>12,54%</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>24,96%</t>
+          <t>13,2%</t>
         </is>
       </c>
     </row>
@@ -15795,32 +15795,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>151039</t>
+          <t>161859</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>118386</t>
+          <t>139707</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>177154</t>
+          <t>186528</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -15830,32 +15830,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>276760</t>
+          <t>305890</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>226646</t>
+          <t>280808</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>308848</t>
+          <t>330548</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -15865,32 +15865,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>427799</t>
+          <t>467749</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>371618</t>
+          <t>435067</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>472988</t>
+          <t>504693</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,94%</t>
         </is>
       </c>
     </row>
@@ -15908,17 +15908,17 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>3459070</t>
+          <t>3531888</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>3459070</t>
+          <t>3531888</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>3459070</t>
+          <t>3531888</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -15943,17 +15943,17 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>3711161</t>
+          <t>3735742</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>3711161</t>
+          <t>3735742</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>3711161</t>
+          <t>3735742</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -15978,17 +15978,17 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>7170231</t>
+          <t>7267629</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>7170231</t>
+          <t>7267629</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>7170231</t>
+          <t>7267629</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
